--- a/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Collegetown_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Collegetown_20260515.xlsx
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>10.25</v>
       </c>
       <c r="E9" t="n">
-        <v>20.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>23.75</v>
       </c>
       <c r="E11" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
